--- a/Level1_Horizontal_RotatorCuff.xlsx
+++ b/Level1_Horizontal_RotatorCuff.xlsx
@@ -547,7 +547,7 @@
     <row r="2" ht="30" customHeight="1" s="26">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Choose 2 sets from 2 DIFFERENT exercise categories. Alternate the 2 categories every week — never the same categories two weeks in a row — so the programming cycles through all categories over time. The prescription is the same on every day of every sub-level of Level 1.</t>
+          <t>Choose 2 DIFFERENT categories and do 2 sets of each (4 sets total). Alternate the 2 categories every week — never the same categories two weeks in a row — so the programming cycles through all categories over time. The prescription is the same on every day of every sub-level of Level 1.</t>
         </is>
       </c>
       <c r="H2" s="3" t="n"/>
